--- a/human_resources_forms/016_e_commerce_digital_marketing_interview_form--human_resources_forms.xlsx
+++ b/human_resources_forms/016_e_commerce_digital_marketing_interview_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1154,8 +1154,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option':_'facebook'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option': 'Facebook'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option':_'twitter'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option': 'Twitter'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option':_'linkedin'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option': 'LinkedIn'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option':_'other'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option': 'Other'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_'amazon'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': 'Amazon'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option':_'ebay'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option': 'eBay'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option':_'etsy'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option': 'Etsy'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option':_'shopify'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option': 'Shopify'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option':_'other'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option': 'Other'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option':_'electronics'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option': 'Electronics'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option':_'fashion'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option': 'Fashion'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option':_'home_and_garden'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option': 'Home and Garden'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option':_'beauty_and_personal_care'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option': 'Beauty and Personal Care'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option':_'sports'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option': 'Sports'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option':_'food_and_beverage'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option': 'Food and Beverage'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option':_'other'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option': 'Other'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option':_'other'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option': 'Other'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
